--- a/examples/output/xlsx/05-template.xlsx
+++ b/examples/output/xlsx/05-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice" sheetId="1" r:id="Rb41ef1fab7c04d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice" sheetId="1" r:id="Rf96364dd24684763"/>
   </x:sheets>
 </x:workbook>
 </file>
